--- a/water_quality.xlsx
+++ b/water_quality.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f241abdfd3558b0f/Desktop/tgos_mapo/20260512測試/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jewei\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FBD394F-5D8A-438F-A108-CF06B9F53BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375DFC92-F951-4E79-A01A-994A2768D655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{596FF330-859F-491B-B8CB-782099558C5E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="6" xr2:uid="{596FF330-859F-491B-B8CB-782099558C5E}"/>
   </bookViews>
   <sheets>
-    <sheet name="烏石漁港" sheetId="2" r:id="rId1"/>
+    <sheet name="烏石港" sheetId="2" r:id="rId1"/>
     <sheet name="梗枋漁港" sheetId="3" r:id="rId2"/>
     <sheet name="大溪第一漁港" sheetId="4" r:id="rId3"/>
     <sheet name="大溪第二漁港" sheetId="5" r:id="rId4"/>
-    <sheet name="番薯寮漁港" sheetId="6" r:id="rId5"/>
+    <sheet name="蕃薯寮漁港" sheetId="6" r:id="rId5"/>
     <sheet name="大里漁港" sheetId="7" r:id="rId6"/>
-    <sheet name="桶盤崛漁港" sheetId="8" r:id="rId7"/>
+    <sheet name="桶盤堀漁港" sheetId="8" r:id="rId7"/>
     <sheet name="石城漁港" sheetId="9" r:id="rId8"/>
     <sheet name="蘇澳港" sheetId="10" r:id="rId9"/>
     <sheet name="南方澳第三漁港" sheetId="11" r:id="rId10"/>
